--- a/Smoke-tests/Smoke2 - Авторизация.xlsx
+++ b/Smoke-tests/Smoke2 - Авторизация.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yaros\Documents\Smoke-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A5F388-19D5-4433-B3D7-204934BEE1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A47F69-9A4C-402A-B37F-F385126D9BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3330" yWindow="4065" windowWidth="23160" windowHeight="11685" xr2:uid="{60CBE097-ABDC-4BE2-8156-EB43CE3551D6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{60CBE097-ABDC-4BE2-8156-EB43CE3551D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -77,16 +77,10 @@
     <t>4 мин</t>
   </si>
   <si>
-    <t>Нажать на кнопку «Войти» .</t>
-  </si>
-  <si>
     <t>Отображается окно "Вход"</t>
   </si>
   <si>
     <t>Тестовые данные</t>
-  </si>
-  <si>
-    <t>Заполнить поле Эл.почта валидными данными</t>
   </si>
   <si>
     <t>Test1@mail.ru</t>
@@ -96,28 +90,34 @@
 </t>
   </si>
   <si>
-    <t>Заполнить поле Пароль валидными данными ()</t>
-  </si>
-  <si>
-    <t>Нажать на иконку глазика</t>
-  </si>
-  <si>
     <t>Иконка глазика теперь зачеркнута, отображается введенный пароль</t>
   </si>
   <si>
-    <t xml:space="preserve">Нажать на иконку глазика </t>
-  </si>
-  <si>
     <t>Пароль не виден, иконка глазика вернулась в изначальное состояние</t>
   </si>
   <si>
-    <t>Нажать на кнопку "Войти"</t>
-  </si>
-  <si>
     <t>Окно "Вы успешно авторизованы"</t>
   </si>
   <si>
     <t>Авторизация покупателя</t>
+  </si>
+  <si>
+    <t>1) Нажать на кнопку «Войти» .</t>
+  </si>
+  <si>
+    <t>2) Заполнить поле Эл.почта валидными данными</t>
+  </si>
+  <si>
+    <t>3) Заполнить поле Пароль валидными данными ()</t>
+  </si>
+  <si>
+    <t>4) Нажать на иконку глазика</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5) Нажать на иконку глазика </t>
+  </si>
+  <si>
+    <t>6) Нажать на кнопку "Войти"</t>
   </si>
 </sst>
 </file>
@@ -659,7 +659,7 @@
         <v>4</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>5</v>
@@ -679,17 +679,17 @@
         <v>10</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I2" s="7" t="s">
         <v>12</v>
@@ -702,13 +702,13 @@
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
       <c r="F3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>16</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>18</v>
       </c>
       <c r="I3" s="7"/>
     </row>
@@ -719,13 +719,13 @@
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I4" s="7"/>
     </row>
@@ -736,11 +736,11 @@
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I5" s="7"/>
     </row>
@@ -751,11 +751,11 @@
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I6" s="7"/>
     </row>
@@ -766,11 +766,11 @@
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I7" s="7"/>
     </row>
